--- a/ig/main/CodeSystem-900000000000207008-20240301.xlsx
+++ b/ig/main/CodeSystem-900000000000207008-20240301.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-21T15:27:12+00:00</t>
+    <t>2024-10-22T10:27:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-900000000000207008-20240301.xlsx
+++ b/ig/main/CodeSystem-900000000000207008-20240301.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-22T10:27:39+00:00</t>
+    <t>2024-10-22T15:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-900000000000207008-20240301.xlsx
+++ b/ig/main/CodeSystem-900000000000207008-20240301.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-22T15:26:51+00:00</t>
+    <t>2024-10-23T04:30:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-900000000000207008-20240301.xlsx
+++ b/ig/main/CodeSystem-900000000000207008-20240301.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-23T04:30:12+00:00</t>
+    <t>2024-10-23T15:28:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-900000000000207008-20240301.xlsx
+++ b/ig/main/CodeSystem-900000000000207008-20240301.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-23T15:28:11+00:00</t>
+    <t>2024-10-24T04:29:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-900000000000207008-20240301.xlsx
+++ b/ig/main/CodeSystem-900000000000207008-20240301.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-24T04:29:26+00:00</t>
+    <t>2024-10-24T15:26:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-900000000000207008-20240301.xlsx
+++ b/ig/main/CodeSystem-900000000000207008-20240301.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-24T15:26:50+00:00</t>
+    <t>2024-10-25T04:31:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-900000000000207008-20240301.xlsx
+++ b/ig/main/CodeSystem-900000000000207008-20240301.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-25T04:31:08+00:00</t>
+    <t>2024-10-25T07:51:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-900000000000207008-20240301.xlsx
+++ b/ig/main/CodeSystem-900000000000207008-20240301.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-25T07:51:12+00:00</t>
+    <t>2024-10-25T15:09:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-900000000000207008-20240301.xlsx
+++ b/ig/main/CodeSystem-900000000000207008-20240301.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-25T15:09:58+00:00</t>
+    <t>2024-10-26T04:29:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-900000000000207008-20240301.xlsx
+++ b/ig/main/CodeSystem-900000000000207008-20240301.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-26T04:29:20+00:00</t>
+    <t>2024-10-26T08:59:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-900000000000207008-20240301.xlsx
+++ b/ig/main/CodeSystem-900000000000207008-20240301.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-26T08:59:08+00:00</t>
+    <t>2024-10-26T09:30:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-900000000000207008-20240301.xlsx
+++ b/ig/main/CodeSystem-900000000000207008-20240301.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-26T09:30:33+00:00</t>
+    <t>2024-10-26T10:09:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-900000000000207008-20240301.xlsx
+++ b/ig/main/CodeSystem-900000000000207008-20240301.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-26T10:09:34+00:00</t>
+    <t>2024-10-26T12:22:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
